--- a/tame_output/ON/bt/strategyON_20231211.xlsx
+++ b/tame_output/ON/bt/strategyON_20231211.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>82.9%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-342.8%</t>
+          <t>-368.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>477.1%</t>
+          <t>477.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-161.4%</t>
+          <t>-160.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-78.8%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-125.6%</t>
+          <t>-135.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-7.9%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-6.4%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>119.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
     </row>
@@ -41996,10 +41996,10 @@
         <v>2.992474709334104</v>
       </c>
       <c r="D1760" t="n">
-        <v>-1.874468351035248</v>
+        <v>-2.127025399757956</v>
       </c>
       <c r="E1760" t="n">
-        <v>2.242330944606258</v>
+        <v>2.141308125117174</v>
       </c>
       <c r="F1760" t="n">
         <v>0.8130998247229593</v>
@@ -42019,10 +42019,10 @@
         <v>3.010249418375564</v>
       </c>
       <c r="D1761" t="n">
-        <v>-1.867370350067746</v>
+        <v>-2.119927398790455</v>
       </c>
       <c r="E1761" t="n">
-        <v>2.262944854034719</v>
+        <v>2.161922034545635</v>
       </c>
       <c r="F1761" t="n">
         <v>0.8132070228343352</v>
@@ -42042,10 +42042,10 @@
         <v>3.010722978056604</v>
       </c>
       <c r="D1762" t="n">
-        <v>-1.86616728377164</v>
+        <v>-2.118724332494348</v>
       </c>
       <c r="E1762" t="n">
-        <v>2.263899640234202</v>
+        <v>2.162876820745118</v>
       </c>
       <c r="F1762" t="n">
         <v>0.8132070228343352</v>
@@ -42065,10 +42065,10 @@
         <v>3.016062350193502</v>
       </c>
       <c r="D1763" t="n">
-        <v>-1.863814236438395</v>
+        <v>-2.116371285161103</v>
       </c>
       <c r="E1763" t="n">
-        <v>2.270180231304397</v>
+        <v>2.169157411815314</v>
       </c>
       <c r="F1763" t="n">
         <v>0.8155600701675807</v>
@@ -42088,10 +42088,10 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-1.862697954447168</v>
+        <v>-2.115255003169877</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.285203768936937</v>
+        <v>2.184180949447854</v>
       </c>
       <c r="F1764" t="n">
         <v>0.8166763521588069</v>
@@ -42111,10 +42111,10 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-1.858959998386113</v>
+        <v>-2.111517047108821</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.286623932225007</v>
+        <v>2.185601112735923</v>
       </c>
       <c r="F1765" t="n">
         <v>0.8190528044394316</v>
@@ -42134,10 +42134,10 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-1.85046285272498</v>
+        <v>-2.103019901447688</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.288338214987554</v>
+        <v>2.187315395498471</v>
       </c>
       <c r="F1766" t="n">
         <v>0.8190528044394316</v>
@@ -42157,10 +42157,10 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-1.850154892640255</v>
+        <v>-2.102711941362964</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.29284997470229</v>
+        <v>2.191827155213206</v>
       </c>
       <c r="F1767" t="n">
         <v>0.8202345185321317</v>
@@ -42180,10 +42180,10 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-1.848373130269664</v>
+        <v>-2.100930178992372</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.295222976827401</v>
+        <v>2.194200157338317</v>
       </c>
       <c r="F1768" t="n">
         <v>0.8202345185321317</v>
@@ -42203,10 +42203,10 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-1.852450485406755</v>
+        <v>-2.105007534129464</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.308626205036254</v>
+        <v>2.207603385547171</v>
       </c>
       <c r="F1769" t="n">
         <v>0.8202345185321317</v>
@@ -42226,10 +42226,10 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-1.842458404480346</v>
+        <v>-2.095015453203055</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.310937472070952</v>
+        <v>2.209914652581868</v>
       </c>
       <c r="F1770" t="n">
         <v>0.8302265994585408</v>
@@ -42249,10 +42249,10 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-1.843014159536384</v>
+        <v>-2.095571208259093</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.313616979945128</v>
+        <v>2.212594160456044</v>
       </c>
       <c r="F1771" t="n">
         <v>0.828619185697463</v>
@@ -42272,10 +42272,10 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-1.846228511949696</v>
+        <v>-2.098785560672404</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.31785622811895</v>
+        <v>2.216833408629867</v>
       </c>
       <c r="F1772" t="n">
         <v>0.828619185697463</v>
@@ -42295,10 +42295,10 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-1.863236757352305</v>
+        <v>-2.115793806075013</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.312130502595637</v>
+        <v>2.211107683106554</v>
       </c>
       <c r="F1773" t="n">
         <v>0.8316183207104367</v>
@@ -42318,10 +42318,10 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-1.84427703490095</v>
+        <v>-2.096834083623659</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.320464253747452</v>
+        <v>2.219441434258369</v>
       </c>
       <c r="F1774" t="n">
         <v>0.8316183207104367</v>
@@ -42341,10 +42341,10 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-1.843042310298141</v>
+        <v>-2.09559935902085</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.319193741052157</v>
+        <v>2.218170921563073</v>
       </c>
       <c r="F1775" t="n">
         <v>0.8316183207104367</v>
@@ -42364,10 +42364,10 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-1.85307657412179</v>
+        <v>-2.105633622844499</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.318747645359559</v>
+        <v>2.217724825870476</v>
       </c>
       <c r="F1776" t="n">
         <v>0.8316183207104367</v>
@@ -42387,10 +42387,10 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-1.858115572419657</v>
+        <v>-2.110672621142366</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.340714007930022</v>
+        <v>2.239691188440938</v>
       </c>
       <c r="F1777" t="n">
         <v>0.8265793224125699</v>
@@ -42410,10 +42410,10 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-1.848295854259106</v>
+        <v>-2.100852902981815</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.342110606681471</v>
+        <v>2.241087787192388</v>
       </c>
       <c r="F1778" t="n">
         <v>0.8330092626292573</v>
@@ -42433,10 +42433,10 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-1.846494227420152</v>
+        <v>-2.099051276142861</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.328079819420679</v>
+        <v>2.227056999931595</v>
       </c>
       <c r="F1779" t="n">
         <v>0.8330092626292573</v>
@@ -42456,10 +42456,10 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-1.845505545675984</v>
+        <v>-2.098062594398693</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.326589048434018</v>
+        <v>2.225566228944934</v>
       </c>
       <c r="F1780" t="n">
         <v>0.8330092626292573</v>
@@ -42479,10 +42479,10 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-1.837509191154446</v>
+        <v>-2.090066239877155</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.331761216698474</v>
+        <v>2.23073839720939</v>
       </c>
       <c r="F1781" t="n">
         <v>0.8410056171507959</v>
@@ -42502,10 +42502,10 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-1.832525440482537</v>
+        <v>-2.085082489205246</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.345593297558149</v>
+        <v>2.244570478069065</v>
       </c>
       <c r="F1782" t="n">
         <v>0.8459893678227046</v>
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-1.826139301532981</v>
+        <v>-2.078696350255691</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.35487595614976</v>
+        <v>2.253853136660676</v>
       </c>
       <c r="F1783" t="n">
         <v>0.8459893678227046</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-1.837944651851614</v>
+        <v>-2.090501700574323</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.35416990478185</v>
+        <v>2.253147085292766</v>
       </c>
       <c r="F1784" t="n">
         <v>0.834184017504072</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-1.829212841072948</v>
+        <v>-2.081769889795657</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.363610086703205</v>
+        <v>2.262587267214122</v>
       </c>
       <c r="F1785" t="n">
         <v>0.8429158282827383</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-1.822875954428496</v>
+        <v>-2.075433003151204</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.361455660308972</v>
+        <v>2.260432840819888</v>
       </c>
       <c r="F1786" t="n">
         <v>0.8429158282827383</v>
@@ -42617,10 +42617,10 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-1.820341506701127</v>
+        <v>-2.072898555423836</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.372432097202113</v>
+        <v>2.271409277713029</v>
       </c>
       <c r="F1787" t="n">
         <v>0.8429158282827383</v>
@@ -42640,10 +42640,10 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-1.820417405681732</v>
+        <v>-2.072974454404441</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.364816417802781</v>
+        <v>2.263793598313697</v>
       </c>
       <c r="F1788" t="n">
         <v>0.8436790889720651</v>
@@ -42663,10 +42663,10 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-1.830919595241079</v>
+        <v>-2.083476643963787</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.338380117769415</v>
+        <v>2.237357298280332</v>
       </c>
       <c r="F1789" t="n">
         <v>0.8331768994127184</v>
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-1.832752857920195</v>
+        <v>-2.085309906642903</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.338347652543891</v>
+        <v>2.237324833054807</v>
       </c>
       <c r="F1790" t="n">
         <v>0.8331768994127184</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-1.837761972981779</v>
+        <v>-2.090319021704488</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.336861086348117</v>
+        <v>2.235838266859033</v>
       </c>
       <c r="F1791" t="n">
         <v>0.8321823218541837</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-1.841467529618593</v>
+        <v>-2.094024578341302</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.334606588933756</v>
+        <v>2.233583769444672</v>
       </c>
       <c r="F1792" t="n">
         <v>0.8303126465965488</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-1.840235204261228</v>
+        <v>-2.092792252983937</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.335519371139021</v>
+        <v>2.234496551649938</v>
       </c>
       <c r="F1793" t="n">
         <v>0.8309430229685864</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-1.829907207245376</v>
+        <v>-2.082464255968084</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.343780478109576</v>
+        <v>2.242757658620492</v>
       </c>
       <c r="F1794" t="n">
         <v>0.8412710199844385</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-1.82979087209782</v>
+        <v>-2.082347920820529</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.350347672370435</v>
+        <v>2.249324852881351</v>
       </c>
       <c r="F1795" t="n">
         <v>0.8413873551319943</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-1.831636281674688</v>
+        <v>-2.084193330397396</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.346583478985076</v>
+        <v>2.245560659495993</v>
       </c>
       <c r="F1796" t="n">
         <v>0.8413873551319943</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-1.830137849149589</v>
+        <v>-2.082694897872297</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.347121139856249</v>
+        <v>2.246098320367166</v>
       </c>
       <c r="F1797" t="n">
         <v>0.8428857876570932</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-1.838202101342323</v>
+        <v>-2.090759150065031</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.345173416922467</v>
+        <v>2.244150597433384</v>
       </c>
       <c r="F1798" t="n">
         <v>0.8348215354643593</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-1.839532068803535</v>
+        <v>-2.092089117526243</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.344641429937982</v>
+        <v>2.243618610448899</v>
       </c>
       <c r="F1799" t="n">
         <v>0.8348215354643593</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-1.611667386070024</v>
+        <v>-1.864224434792732</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.438003776138549</v>
+        <v>2.336980956649465</v>
       </c>
       <c r="F1800" t="n">
         <v>0.8348215354643593</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-1.363565822202807</v>
+        <v>-1.616122870925515</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.544778998030528</v>
+        <v>2.443756178541444</v>
       </c>
       <c r="F1801" t="n">
         <v>0.8348215354643593</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-1.066727422809477</v>
+        <v>-1.319284471532185</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.664937368761317</v>
+        <v>2.563914549272234</v>
       </c>
       <c r="F1802" t="n">
         <v>0.949676023945487</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-0.7630878659840402</v>
+        <v>-1.015644914706748</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.788070265957178</v>
+        <v>2.687047446468095</v>
       </c>
       <c r="F1803" t="n">
         <v>0.949676023945487</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-0.4740672595433316</v>
+        <v>-0.7266243082660395</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.899617929982919</v>
+        <v>2.798595110493836</v>
       </c>
       <c r="F1804" t="n">
         <v>0.949676023945487</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-0.1893473322794345</v>
+        <v>-0.4419043810021424</v>
       </c>
       <c r="E1805" t="n">
-        <v>3.018726040232496</v>
+        <v>2.917703220743412</v>
       </c>
       <c r="F1805" t="n">
         <v>1.234395951209384</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>0.0944143372121059</v>
+        <v>-0.158142711510602</v>
       </c>
       <c r="E1806" t="n">
-        <v>3.137542871202919</v>
+        <v>3.036520051713835</v>
       </c>
       <c r="F1806" t="n">
         <v>1.234395951209384</v>
@@ -43077,10 +43077,10 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>0.3560627316047466</v>
+        <v>0.1035056828820387</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.235444816406609</v>
+        <v>3.134421996917525</v>
       </c>
       <c r="F1807" t="n">
         <v>1.496044345602025</v>
@@ -43094,22 +43094,22 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>2.994405405884044</v>
+        <v>3.064449544071872</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>0.6173571815622787</v>
+        <v>0.635945750148055</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.337426271405734</v>
+        <v>3.344861698840044</v>
       </c>
       <c r="F1808" t="n">
-        <v>1.757338795559557</v>
+        <v>2.028484412868041</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.145243100430306</v>
+        <v>4.307930470815395</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231211.xlsx
+++ b/tame_output/ON/bt/strategyON_20231211.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>477.6%</t>
+          <t>477.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-77.4%</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>119.8%</t>
+          <t>120.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>0.635945750148055</v>
+        <v>0.6502072169979932</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.344861698840044</v>
+        <v>3.35056628558002</v>
       </c>
       <c r="F1808" t="n">
-        <v>2.028484412868041</v>
+        <v>2.042745879717979</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.307930470815395</v>
+        <v>4.316487350925359</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231211.xlsx
+++ b/tame_output/ON/bt/strategyON_20231211.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>477.7%</t>
+          <t>476.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-100.6%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>75.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-28.2%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>0.6502072169979932</v>
+        <v>0.4176721210213711</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.35056628558002</v>
+        <v>3.257552247189371</v>
       </c>
       <c r="F1808" t="n">
-        <v>2.042745879717979</v>
+        <v>1.810210783741357</v>
       </c>
       <c r="G1808" t="n">
-        <v>4.316487350925359</v>
+        <v>4.176966293339385</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231211.xlsx
+++ b/tame_output/ON/bt/strategyON_20231211.xlsx
@@ -42013,7 +42013,7 @@
         <v>45223</v>
       </c>
       <c r="B1761" t="n">
-        <v>3.046980105223825</v>
+        <v>3.046980105223824</v>
       </c>
       <c r="C1761" t="n">
         <v>3.010249418375564</v>
@@ -42036,7 +42036,7 @@
         <v>45224</v>
       </c>
       <c r="B1762" t="n">
-        <v>3.070330524157812</v>
+        <v>3.070330524157811</v>
       </c>
       <c r="C1762" t="n">
         <v>3.010722978056604</v>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336375</v>
+        <v>3.050895742336374</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320088</v>
+        <v>3.049222094320087</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42105,7 +42105,7 @@
         <v>45227</v>
       </c>
       <c r="B1765" t="n">
-        <v>3.046605534538362</v>
+        <v>3.046605534538361</v>
       </c>
       <c r="C1765" t="n">
         <v>3.030564355893199</v>
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477762</v>
+        <v>3.055423383477761</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42151,7 +42151,7 @@
         <v>45229</v>
       </c>
       <c r="B1767" t="n">
-        <v>3.053640504831979</v>
+        <v>3.053640504831978</v>
       </c>
       <c r="C1767" t="n">
         <v>3.033268356072139</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571591</v>
+        <v>3.068246518571589</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968025</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066014</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293023</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239776</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.12829875500301</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167863</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216944</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.13201899645404</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780869</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537932</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373821</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502549</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728032</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702056</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823382</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524823</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068703</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083878</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666735</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.1634320910971</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.16927921276226</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963481</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583696</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742726</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589526</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872959</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946331</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336487</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308505</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.064449544071872</v>
+        <v>3.064449544071871</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
